--- a/oi_funding_history.xlsx
+++ b/oi_funding_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,35 +489,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>296345.1484569854</v>
+        <v>303737.1261440159</v>
       </c>
       <c r="D2" t="n">
-        <v>19286468241.24391</v>
+        <v>19396898902.62903</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.008162060285127372</v>
+        <v>0.007190880499901301</v>
       </c>
       <c r="F2" t="n">
-        <v>65081.1</v>
+        <v>63860.81</v>
       </c>
       <c r="G2" t="n">
-        <v>-32.62892999999994</v>
+        <v>106.7992899999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1114.538999999999</v>
+        <v>-74.93799999999942</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Nötr Pozitif</t>
+          <t>Pozitif</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
+          <t>Spot Long / Perp Short (Diverjans)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -544,35 +544,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>296221.0877701452</v>
+        <v>303813.5467904178</v>
       </c>
       <c r="D3" t="n">
-        <v>19228063310.25457</v>
+        <v>19398078738.00908</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.008072423720466754</v>
+        <v>0.007075612017746235</v>
       </c>
       <c r="F3" t="n">
-        <v>64911.19</v>
+        <v>63848.63</v>
       </c>
       <c r="G3" t="n">
-        <v>-73.27987999999996</v>
+        <v>75.18262999999988</v>
       </c>
       <c r="H3" t="n">
-        <v>817.7839999999987</v>
+        <v>-198.1839999999995</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Nötr Pozitif</t>
+          <t>Pozitif</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
+          <t>Spot Long / Perp Short (Diverjans)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -599,35 +599,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>295463.4410687479</v>
+        <v>303844.5988269334</v>
       </c>
       <c r="D4" t="n">
-        <v>19182045020.08673</v>
+        <v>19394260974.6077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.00825694259351221</v>
+        <v>0.007026063361651355</v>
       </c>
       <c r="F4" t="n">
-        <v>64921.89</v>
+        <v>63829.54</v>
       </c>
       <c r="G4" t="n">
-        <v>-51.63132999999996</v>
+        <v>84.34961999999987</v>
       </c>
       <c r="H4" t="n">
-        <v>566.9389999999985</v>
+        <v>-254.9979999999994</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nötr Pozitif</t>
+          <t>Pozitif</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
+          <t>Spot Long / Perp Short (Diverjans)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -654,35 +654,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>295410.324923887</v>
+        <v>303854.1902698797</v>
       </c>
       <c r="D5" t="n">
-        <v>19165678326.06393</v>
+        <v>19392484898.06338</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.008247372341852221</v>
+        <v>0.007015572400855962</v>
       </c>
       <c r="F5" t="n">
-        <v>64878.16</v>
+        <v>63821.68</v>
       </c>
       <c r="G5" t="n">
-        <v>-36.00380999999993</v>
+        <v>83.01647999999992</v>
       </c>
       <c r="H5" t="n">
-        <v>209.6159999999993</v>
+        <v>-289.0939999999996</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nötr Pozitif</t>
+          <t>Pozitif</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
+          <t>Spot Long / Perp Short (Diverjans)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -709,35 +709,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>295438.5332690304</v>
+        <v>303777.0201789418</v>
       </c>
       <c r="D6" t="n">
-        <v>19177978773.21254</v>
+        <v>19375150481.93966</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.008140074015724015</v>
+        <v>0.006892312232687779</v>
       </c>
       <c r="F6" t="n">
-        <v>64913.6</v>
+        <v>63780.83</v>
       </c>
       <c r="G6" t="n">
-        <v>1.567750000000075</v>
+        <v>24.3902099999999</v>
       </c>
       <c r="H6" t="n">
-        <v>310.8219999999997</v>
+        <v>-314.7029999999995</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nötr Pozitif</t>
+          <t>Aşırı Pozitif</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
+          <t>Spot Long / Perp Short (Diverjans)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -764,35 +764,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>294945.6007108876</v>
+        <v>303795.3687668931</v>
       </c>
       <c r="D7" t="n">
-        <v>19073545056.22769</v>
+        <v>19351737648.8679</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.007739776837636257</v>
+        <v>0.006714050675583268</v>
       </c>
       <c r="F7" t="n">
-        <v>64668.01</v>
+        <v>63699.91</v>
       </c>
       <c r="G7" t="n">
-        <v>-89.96589999999983</v>
+        <v>42.66162999999989</v>
       </c>
       <c r="H7" t="n">
-        <v>-324.6310000000003</v>
+        <v>-398.9959999999996</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Nötr Pozitif</t>
+          <t>Aşırı Pozitif</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -802,17 +802,1832 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>303624.631113503</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19317118229.56026</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.00678630921661464</v>
+      </c>
+      <c r="F8" t="n">
+        <v>63621.71</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3460899999999185</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-657.7179999999996</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>303260.0560202862</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19304228115.40997</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.006949922615906047</v>
+      </c>
+      <c r="F9" t="n">
+        <v>63655.69</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.46390999999986</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-557.6139999999998</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>303389.7986579479</v>
+      </c>
+      <c r="D10" t="n">
+        <v>19304962905.52603</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.00716063343273675</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63630.89</v>
+      </c>
+      <c r="G10" t="n">
+        <v>92.65231999999986</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-532.5639999999999</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>303295.4924267859</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19346227685.64444</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.007845724659507624</v>
+      </c>
+      <c r="F11" t="n">
+        <v>63786.73</v>
+      </c>
+      <c r="G11" t="n">
+        <v>212.7724899999998</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-336.955999999999</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>303342.8705915117</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19331813635.64409</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.007830159125949034</v>
+      </c>
+      <c r="F12" t="n">
+        <v>63729.25</v>
+      </c>
+      <c r="G12" t="n">
+        <v>273.0051599999998</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-467.7109999999991</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>303429.6208165414</v>
+      </c>
+      <c r="D13" t="n">
+        <v>19330090194.48506</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0.007783778433581577</v>
+      </c>
+      <c r="F13" t="n">
+        <v>63705.35</v>
+      </c>
+      <c r="G13" t="n">
+        <v>341.7306699999998</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-552.0339999999992</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>303317.3660405544</v>
+      </c>
+      <c r="D14" t="n">
+        <v>19344568526.06398</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.00766837500551763</v>
+      </c>
+      <c r="F14" t="n">
+        <v>63776.66</v>
+      </c>
+      <c r="G14" t="n">
+        <v>411.0508799999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-366.2589999999989</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>302967.3469621006</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19330867928.99847</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.007191206552286973</v>
+      </c>
+      <c r="F15" t="n">
+        <v>63805.12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>423.8068999999998</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-112.024999999999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>303100.4142402763</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19343262235.98595</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0.007460122751581946</v>
+      </c>
+      <c r="F16" t="n">
+        <v>63818</v>
+      </c>
+      <c r="G16" t="n">
+        <v>429.2955099999998</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-121.022999999999</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>303067.2463305567</v>
+      </c>
+      <c r="D17" t="n">
+        <v>19332053508.93355</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.007191705260099932</v>
+      </c>
+      <c r="F17" t="n">
+        <v>63788</v>
+      </c>
+      <c r="G17" t="n">
+        <v>412.8545499999998</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-255.578999999999</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>303062.7706376919</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19333528808.13449</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.007207331631729812</v>
+      </c>
+      <c r="F18" t="n">
+        <v>63793.81</v>
+      </c>
+      <c r="G18" t="n">
+        <v>409.2874699999998</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-130.3249999999987</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>302987.6207449413</v>
+      </c>
+      <c r="D19" t="n">
+        <v>19349483302.42346</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.007086663022226652</v>
+      </c>
+      <c r="F19" t="n">
+        <v>63862.29</v>
+      </c>
+      <c r="G19" t="n">
+        <v>416.0019699999998</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-103.2069999999987</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>302735.2772682512</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19355924875.64473</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0.007233446185459706</v>
+      </c>
+      <c r="F20" t="n">
+        <v>63936.8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>433.9765499999998</v>
+      </c>
+      <c r="H20" t="n">
+        <v>299.6400000000015</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>302702.2398561646</v>
+      </c>
+      <c r="D21" t="n">
+        <v>19355401755.99487</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0.007286388170753836</v>
+      </c>
+      <c r="F21" t="n">
+        <v>63942.05</v>
+      </c>
+      <c r="G21" t="n">
+        <v>434.3575199999998</v>
+      </c>
+      <c r="H21" t="n">
+        <v>265.6530000000009</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>302294.1385421361</v>
+      </c>
+      <c r="D22" t="n">
+        <v>19359684459.35029</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0.007338052512473144</v>
+      </c>
+      <c r="F22" t="n">
+        <v>64042.54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>445.6735899999998</v>
+      </c>
+      <c r="H22" t="n">
+        <v>249.3240000000012</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>Düşüyor</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>302279.7314662891</v>
+      </c>
+      <c r="D23" t="n">
+        <v>19378793871.42335</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0.007040323260779922</v>
+      </c>
+      <c r="F23" t="n">
+        <v>64108.81</v>
+      </c>
+      <c r="G23" t="n">
+        <v>505.0183599999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>370.1110000000015</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>301616.7033512847</v>
+      </c>
+      <c r="D24" t="n">
+        <v>19340760903.68457</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0.006958681511046636</v>
+      </c>
+      <c r="F24" t="n">
+        <v>64123.64</v>
+      </c>
+      <c r="G24" t="n">
+        <v>202.5172499999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>649.3720000000005</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>301353.5105475997</v>
+      </c>
+      <c r="D25" t="n">
+        <v>19307116713.76362</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>0.006872732011318173</v>
+      </c>
+      <c r="F25" t="n">
+        <v>64068</v>
+      </c>
+      <c r="G25" t="n">
+        <v>76.36994999999996</v>
+      </c>
+      <c r="H25" t="n">
+        <v>540.0760000000007</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>301540.6224775896</v>
+      </c>
+      <c r="D26" t="n">
+        <v>19342431783.44908</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>0.006861467163347502</v>
+      </c>
+      <c r="F26" t="n">
+        <v>64145.36</v>
+      </c>
+      <c r="G26" t="n">
+        <v>90.27937999999995</v>
+      </c>
+      <c r="H26" t="n">
+        <v>784.7780000000009</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>301572.0075572577</v>
+      </c>
+      <c r="D27" t="n">
+        <v>19345440178.30795</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0.006650328299412574</v>
+      </c>
+      <c r="F27" t="n">
+        <v>64148.66</v>
+      </c>
+      <c r="G27" t="n">
+        <v>54.06252999999987</v>
+      </c>
+      <c r="H27" t="n">
+        <v>608.8840000000007</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>301273.784094642</v>
+      </c>
+      <c r="D28" t="n">
+        <v>19323697499.09249</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>0.006757654848080424</v>
+      </c>
+      <c r="F28" t="n">
+        <v>64139.99</v>
+      </c>
+      <c r="G28" t="n">
+        <v>60.26102000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>663.7940000000015</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>301115.8828319952</v>
+      </c>
+      <c r="D29" t="n">
+        <v>19316580872.51366</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0.006677882851911259</v>
+      </c>
+      <c r="F29" t="n">
+        <v>64149.99</v>
+      </c>
+      <c r="G29" t="n">
+        <v>53.67986000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>582.4580000000014</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>300882.5720010658</v>
+      </c>
+      <c r="D30" t="n">
+        <v>19320271713.33244</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>0.006508854538607164</v>
+      </c>
+      <c r="F30" t="n">
+        <v>64212</v>
+      </c>
+      <c r="G30" t="n">
+        <v>111.8387</v>
+      </c>
+      <c r="H30" t="n">
+        <v>674.6360000000016</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>300508.0669031474</v>
+      </c>
+      <c r="D31" t="n">
+        <v>19303974095.03033</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0.006191116896283788</v>
+      </c>
+      <c r="F31" t="n">
+        <v>64237.79</v>
+      </c>
+      <c r="G31" t="n">
+        <v>88.45165000000003</v>
+      </c>
+      <c r="H31" t="n">
+        <v>829.4370000000015</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>300255.2051744295</v>
+      </c>
+      <c r="D32" t="n">
+        <v>19297402036.56059</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>0.005957255407340198</v>
+      </c>
+      <c r="F32" t="n">
+        <v>64270</v>
+      </c>
+      <c r="G32" t="n">
+        <v>79.53007000000005</v>
+      </c>
+      <c r="H32" t="n">
+        <v>904.9710000000013</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>299831.5790364502</v>
+      </c>
+      <c r="D33" t="n">
+        <v>19276325130.3587</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0.00578934657906524</v>
+      </c>
+      <c r="F33" t="n">
+        <v>64290.51</v>
+      </c>
+      <c r="G33" t="n">
+        <v>105.79258</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1025.227000000001</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>298912.8558977589</v>
+      </c>
+      <c r="D34" t="n">
+        <v>19160314063.04634</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>0.005509594744381846</v>
+      </c>
+      <c r="F34" t="n">
+        <v>64100</v>
+      </c>
+      <c r="G34" t="n">
+        <v>69.77556000000016</v>
+      </c>
+      <c r="H34" t="n">
+        <v>976.6420000000028</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Long Squeeze (Zayıf Temel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>299966.7274989219</v>
+      </c>
+      <c r="D35" t="n">
+        <v>19207763462.60392</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>0.005258273671212605</v>
+      </c>
+      <c r="F35" t="n">
+        <v>64032.98</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-33.75452999999993</v>
+      </c>
+      <c r="H35" t="n">
+        <v>367.1140000000007</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>299476.5245367857</v>
+      </c>
+      <c r="D36" t="n">
+        <v>19203345161.93329</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0.00546439965843135</v>
+      </c>
+      <c r="F36" t="n">
+        <v>64123.04</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-55.45206999999983</v>
+      </c>
+      <c r="H36" t="n">
+        <v>819.7230000000034</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>300113.9222094453</v>
+      </c>
+      <c r="D37" t="n">
+        <v>19204292883.32163</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>0.00536412911912231</v>
+      </c>
+      <c r="F37" t="n">
+        <v>63990.01</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-85.24768999999984</v>
+      </c>
+      <c r="H37" t="n">
+        <v>521.7400000000035</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>300521.0060261394</v>
+      </c>
+      <c r="D38" t="n">
+        <v>19214354463.30213</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>0.005343329351479499</v>
+      </c>
+      <c r="F38" t="n">
+        <v>63936.81</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.18157999999988</v>
+      </c>
+      <c r="H38" t="n">
+        <v>636.7420000000031</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>300628.852932753</v>
+      </c>
+      <c r="D39" t="n">
+        <v>19245179907.17282</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>0.005881895531413963</v>
+      </c>
+      <c r="F39" t="n">
+        <v>64016.41</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-65.18444999999986</v>
+      </c>
+      <c r="H39" t="n">
+        <v>929.6680000000035</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>301347.1415462098</v>
+      </c>
+      <c r="D40" t="n">
+        <v>19190192792.30372</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>0.006256636478825242</v>
+      </c>
+      <c r="F40" t="n">
+        <v>63681.35</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-98.24190999999981</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-81.7039999999979</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Spot Short / Perp Short (Uyumlu)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
         </is>
       </c>
     </row>

--- a/oi_funding_history.xlsx
+++ b/oi_funding_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2631,6 +2631,3086 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>302807.4167652896</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19199201452.58642</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>0.006702806401106149</v>
+      </c>
+      <c r="F41" t="n">
+        <v>63404</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-127.0662799999997</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-300.3409999999965</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Short (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>303369.7375390051</v>
+      </c>
+      <c r="D42" t="n">
+        <v>19267360906.30038</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>0.006968008933015039</v>
+      </c>
+      <c r="F42" t="n">
+        <v>63511.15</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-59.38685999999973</v>
+      </c>
+      <c r="H42" t="n">
+        <v>570.0260000000037</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>303740.5518156303</v>
+      </c>
+      <c r="D43" t="n">
+        <v>19265348942.60446</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>0.0071022668023858</v>
+      </c>
+      <c r="F43" t="n">
+        <v>63426.99</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-6.949109999999735</v>
+      </c>
+      <c r="H43" t="n">
+        <v>520.5620000000038</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>304533.4716680005</v>
+      </c>
+      <c r="D44" t="n">
+        <v>19333669843.6743</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>0.007188089632119965</v>
+      </c>
+      <c r="F44" t="n">
+        <v>63486.19</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-16.00261999999975</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Nötr (Zayıf Sinyal)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>305294.6288669176</v>
+      </c>
+      <c r="D45" t="n">
+        <v>19368336985.4754</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>0.007875505304006707</v>
+      </c>
+      <c r="F45" t="n">
+        <v>63441.46</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.516330000000266</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1202.955000000004</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>306163.9029938632</v>
+      </c>
+      <c r="D46" t="n">
+        <v>19457159972.91935</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>0.007744040702479659</v>
+      </c>
+      <c r="F46" t="n">
+        <v>63551.45</v>
+      </c>
+      <c r="G46" t="n">
+        <v>65.16565000000031</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1442.572000000004</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>306357.4428844011</v>
+      </c>
+      <c r="D47" t="n">
+        <v>19471634851.44035</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>0.007609781609836861</v>
+      </c>
+      <c r="F47" t="n">
+        <v>63558.55</v>
+      </c>
+      <c r="G47" t="n">
+        <v>93.24495000000024</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1647.024000000004</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>306931.310771298</v>
+      </c>
+      <c r="D48" t="n">
+        <v>19483542280.10895</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>0.007161129617993939</v>
+      </c>
+      <c r="F48" t="n">
+        <v>63478.51</v>
+      </c>
+      <c r="G48" t="n">
+        <v>96.2298900000003</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1131.416000000004</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>307176.3124869887</v>
+      </c>
+      <c r="D49" t="n">
+        <v>19510834902.63169</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>0.00713829555310968</v>
+      </c>
+      <c r="F49" t="n">
+        <v>63516.73</v>
+      </c>
+      <c r="G49" t="n">
+        <v>111.8962700000003</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1167.723000000004</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>307216.6381208741</v>
+      </c>
+      <c r="D50" t="n">
+        <v>19512265697.80299</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>0.007123752794519753</v>
+      </c>
+      <c r="F50" t="n">
+        <v>63513.05</v>
+      </c>
+      <c r="G50" t="n">
+        <v>111.9221400000003</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1172.556000000004</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>307310.5742684868</v>
+      </c>
+      <c r="D51" t="n">
+        <v>19502131868.05719</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>0.006782732135872587</v>
+      </c>
+      <c r="F51" t="n">
+        <v>63460.66</v>
+      </c>
+      <c r="G51" t="n">
+        <v>139.7182300000003</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1151.758000000004</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>307456.7373649243</v>
+      </c>
+      <c r="D52" t="n">
+        <v>19524729575.05478</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>0.007066722497619644</v>
+      </c>
+      <c r="F52" t="n">
+        <v>63503.99</v>
+      </c>
+      <c r="G52" t="n">
+        <v>150.8020100000003</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1199.735000000004</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>307510.9946709506</v>
+      </c>
+      <c r="D53" t="n">
+        <v>19528584120.09702</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>0.007407877449535039</v>
+      </c>
+      <c r="F53" t="n">
+        <v>63505.32</v>
+      </c>
+      <c r="G53" t="n">
+        <v>159.5910500000003</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1254.902000000004</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>307656.6086756729</v>
+      </c>
+      <c r="D54" t="n">
+        <v>19525119012.9929</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>0.007810305007058578</v>
+      </c>
+      <c r="F54" t="n">
+        <v>63464</v>
+      </c>
+      <c r="G54" t="n">
+        <v>163.8182700000003</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1291.070000000004</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>307848.9813546354</v>
+      </c>
+      <c r="D55" t="n">
+        <v>19519426334.42481</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>0.008221286825914135</v>
+      </c>
+      <c r="F55" t="n">
+        <v>63405.85</v>
+      </c>
+      <c r="G55" t="n">
+        <v>146.2713300000003</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1206.984000000004</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>308042.7720020564</v>
+      </c>
+      <c r="D56" t="n">
+        <v>19546348907.24441</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>0.008397109214523382</v>
+      </c>
+      <c r="F56" t="n">
+        <v>63453.36</v>
+      </c>
+      <c r="G56" t="n">
+        <v>189.9678200000004</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1284.595000000004</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>308022.3346268698</v>
+      </c>
+      <c r="D57" t="n">
+        <v>19523111656.22376</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>0.008586634404647428</v>
+      </c>
+      <c r="F57" t="n">
+        <v>63382.13</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190.6782400000003</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1141.058000000004</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>308076.1072584635</v>
+      </c>
+      <c r="D58" t="n">
+        <v>19537530520.2233</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>0.008749694893341924</v>
+      </c>
+      <c r="F58" t="n">
+        <v>63417.87</v>
+      </c>
+      <c r="G58" t="n">
+        <v>187.8941300000003</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1180.065000000004</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>308167.6653555642</v>
+      </c>
+      <c r="D59" t="n">
+        <v>19528803752.62451</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>0.00891980873816285</v>
+      </c>
+      <c r="F59" t="n">
+        <v>63370.71</v>
+      </c>
+      <c r="G59" t="n">
+        <v>194.8825100000003</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1196.896000000004</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>308675.041649839</v>
+      </c>
+      <c r="D60" t="n">
+        <v>19556650531.79885</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>0.009061675821469812</v>
+      </c>
+      <c r="F60" t="n">
+        <v>63356.76</v>
+      </c>
+      <c r="G60" t="n">
+        <v>160.8132600000003</v>
+      </c>
+      <c r="H60" t="n">
+        <v>775.572000000004</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>308854.415483215</v>
+      </c>
+      <c r="D61" t="n">
+        <v>19580755321.34902</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>0.009098501704097759</v>
+      </c>
+      <c r="F61" t="n">
+        <v>63398.01</v>
+      </c>
+      <c r="G61" t="n">
+        <v>183.2933000000003</v>
+      </c>
+      <c r="H61" t="n">
+        <v>844.9780000000039</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>308975.5608524038</v>
+      </c>
+      <c r="D62" t="n">
+        <v>19599290008.12905</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>0.009111772384477723</v>
+      </c>
+      <c r="F62" t="n">
+        <v>63433.14</v>
+      </c>
+      <c r="G62" t="n">
+        <v>188.4094100000003</v>
+      </c>
+      <c r="H62" t="n">
+        <v>877.6760000000038</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>308892.7049157748</v>
+      </c>
+      <c r="D63" t="n">
+        <v>19615304547.56153</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>0.009134820489374189</v>
+      </c>
+      <c r="F63" t="n">
+        <v>63502</v>
+      </c>
+      <c r="G63" t="n">
+        <v>245.6523200000003</v>
+      </c>
+      <c r="H63" t="n">
+        <v>933.9840000000038</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>23:41</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>309027.8425975883</v>
+      </c>
+      <c r="D64" t="n">
+        <v>19641973460.25929</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>0.009147685657190634</v>
+      </c>
+      <c r="F64" t="n">
+        <v>63560.53</v>
+      </c>
+      <c r="G64" t="n">
+        <v>264.1931100000003</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1144.168000000004</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>23:56</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>309305.8654518352</v>
+      </c>
+      <c r="D65" t="n">
+        <v>19655954721.25249</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>0.009104344273982936</v>
+      </c>
+      <c r="F65" t="n">
+        <v>63548.6</v>
+      </c>
+      <c r="G65" t="n">
+        <v>250.4459300000003</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Nötr (Zayıf Sinyal)</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>309442.355584014</v>
+      </c>
+      <c r="D66" t="n">
+        <v>19677433202.74034</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>0.008929664223209169</v>
+      </c>
+      <c r="F66" t="n">
+        <v>63589.98</v>
+      </c>
+      <c r="G66" t="n">
+        <v>259.1966900000002</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1397.437000000004</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>309347.2205531783</v>
+      </c>
+      <c r="D67" t="n">
+        <v>19642512191.93797</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>0.008594264846480992</v>
+      </c>
+      <c r="F67" t="n">
+        <v>63496.65</v>
+      </c>
+      <c r="G67" t="n">
+        <v>262.1640900000002</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1242.345000000003</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>00:42</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>309229.5724111608</v>
+      </c>
+      <c r="D68" t="n">
+        <v>19646746268.3569</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>0.008524187375057377</v>
+      </c>
+      <c r="F68" t="n">
+        <v>63534.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>242.6108600000002</v>
+      </c>
+      <c r="H68" t="n">
+        <v>878.4750000000033</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>00:58</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>309488.6007734677</v>
+      </c>
+      <c r="D69" t="n">
+        <v>19661813902.02441</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>0.008421850934498548</v>
+      </c>
+      <c r="F69" t="n">
+        <v>63530.01</v>
+      </c>
+      <c r="G69" t="n">
+        <v>239.6549500000002</v>
+      </c>
+      <c r="H69" t="n">
+        <v>981.1230000000035</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>309648.8574179474</v>
+      </c>
+      <c r="D70" t="n">
+        <v>19668731309.29359</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>0.008207593256445097</v>
+      </c>
+      <c r="F70" t="n">
+        <v>63519.47</v>
+      </c>
+      <c r="G70" t="n">
+        <v>244.1478500000002</v>
+      </c>
+      <c r="H70" t="n">
+        <v>915.0760000000038</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>01:29</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>309746.1341464681</v>
+      </c>
+      <c r="D71" t="n">
+        <v>19670741092.56695</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>0.008037794289508068</v>
+      </c>
+      <c r="F71" t="n">
+        <v>63506.01</v>
+      </c>
+      <c r="G71" t="n">
+        <v>244.3177400000002</v>
+      </c>
+      <c r="H71" t="n">
+        <v>832.1960000000038</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>309647.0954051902</v>
+      </c>
+      <c r="D72" t="n">
+        <v>19631678488.69528</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>0.007806006779417661</v>
+      </c>
+      <c r="F72" t="n">
+        <v>63400.17</v>
+      </c>
+      <c r="G72" t="n">
+        <v>248.6646500000002</v>
+      </c>
+      <c r="H72" t="n">
+        <v>674.9420000000036</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>309813.4031014765</v>
+      </c>
+      <c r="D73" t="n">
+        <v>19652170533.28572</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>0.007615012708239805</v>
+      </c>
+      <c r="F73" t="n">
+        <v>63432.28</v>
+      </c>
+      <c r="G73" t="n">
+        <v>255.2690200000002</v>
+      </c>
+      <c r="H73" t="n">
+        <v>696.639000000004</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>309743.6505646785</v>
+      </c>
+      <c r="D74" t="n">
+        <v>19641817477.36904</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>0.007396848827964491</v>
+      </c>
+      <c r="F74" t="n">
+        <v>63413.14</v>
+      </c>
+      <c r="G74" t="n">
+        <v>262.1065700000002</v>
+      </c>
+      <c r="H74" t="n">
+        <v>541.0600000000042</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>309739.7639570101</v>
+      </c>
+      <c r="D75" t="n">
+        <v>19646951195.07277</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>0.007139777842224479</v>
+      </c>
+      <c r="F75" t="n">
+        <v>63430.51</v>
+      </c>
+      <c r="G75" t="n">
+        <v>331.7584600000002</v>
+      </c>
+      <c r="H75" t="n">
+        <v>588.5630000000042</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>309985.7238770563</v>
+      </c>
+      <c r="D76" t="n">
+        <v>19658352251.68232</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>0.007103981242155372</v>
+      </c>
+      <c r="F76" t="n">
+        <v>63416.96</v>
+      </c>
+      <c r="G76" t="n">
+        <v>353.0734200000001</v>
+      </c>
+      <c r="H76" t="n">
+        <v>573.2510000000042</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>310004.8442999505</v>
+      </c>
+      <c r="D77" t="n">
+        <v>19685304512.99841</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>0.00877254153497091</v>
+      </c>
+      <c r="F77" t="n">
+        <v>63499.99</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-1.57873</v>
+      </c>
+      <c r="H77" t="n">
+        <v>65.58500000000001</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>310269.4549916559</v>
+      </c>
+      <c r="D78" t="n">
+        <v>19739469937.0457</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>0.007957188772542742</v>
+      </c>
+      <c r="F78" t="n">
+        <v>63620.41</v>
+      </c>
+      <c r="G78" t="n">
+        <v>22.65822999999999</v>
+      </c>
+      <c r="H78" t="n">
+        <v>377.1559999999999</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>03:31</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>309723.0037368789</v>
+      </c>
+      <c r="D79" t="n">
+        <v>19688657735.34816</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>0.007266402281383854</v>
+      </c>
+      <c r="F79" t="n">
+        <v>63568.6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>100.03959</v>
+      </c>
+      <c r="H79" t="n">
+        <v>615.4929999999999</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>309889.3322816705</v>
+      </c>
+      <c r="D80" t="n">
+        <v>19690984852.94858</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>0.007062115398097444</v>
+      </c>
+      <c r="F80" t="n">
+        <v>63541.99</v>
+      </c>
+      <c r="G80" t="n">
+        <v>79.08177000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>338.3040000000001</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>309798.630944489</v>
+      </c>
+      <c r="D81" t="n">
+        <v>19690996155.96922</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>0.007620992068683282</v>
+      </c>
+      <c r="F81" t="n">
+        <v>63560.63</v>
+      </c>
+      <c r="G81" t="n">
+        <v>65.33974000000003</v>
+      </c>
+      <c r="H81" t="n">
+        <v>312.3480000000005</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>309944.3901179892</v>
+      </c>
+      <c r="D82" t="n">
+        <v>19714797092.7617</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>0.007710487646084347</v>
+      </c>
+      <c r="F82" t="n">
+        <v>63607.53</v>
+      </c>
+      <c r="G82" t="n">
+        <v>67.88099000000004</v>
+      </c>
+      <c r="H82" t="n">
+        <v>417.2880000000005</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>310429.0345596637</v>
+      </c>
+      <c r="D83" t="n">
+        <v>19697153739.1687</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>0.007410324070863028</v>
+      </c>
+      <c r="F83" t="n">
+        <v>63451.39</v>
+      </c>
+      <c r="G83" t="n">
+        <v>39.66567000000006</v>
+      </c>
+      <c r="H83" t="n">
+        <v>318.0770000000005</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>04:48</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>310580.5864770237</v>
+      </c>
+      <c r="D84" t="n">
+        <v>19702611244.92943</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>0.007482659533602757</v>
+      </c>
+      <c r="F84" t="n">
+        <v>63438</v>
+      </c>
+      <c r="G84" t="n">
+        <v>53.33917000000002</v>
+      </c>
+      <c r="H84" t="n">
+        <v>218.1520000000005</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>310921.2806803461</v>
+      </c>
+      <c r="D85" t="n">
+        <v>19731686314.53613</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>0.007500867295578081</v>
+      </c>
+      <c r="F85" t="n">
+        <v>63462</v>
+      </c>
+      <c r="G85" t="n">
+        <v>62.19220000000007</v>
+      </c>
+      <c r="H85" t="n">
+        <v>167.1890000000009</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>310973.3720259809</v>
+      </c>
+      <c r="D86" t="n">
+        <v>19730327534.93241</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>0.00742359451415903</v>
+      </c>
+      <c r="F86" t="n">
+        <v>63447</v>
+      </c>
+      <c r="G86" t="n">
+        <v>79.60866000000007</v>
+      </c>
+      <c r="H86" t="n">
+        <v>83.17400000000089</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>311137.9284622914</v>
+      </c>
+      <c r="D87" t="n">
+        <v>19732893246.17762</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>0.007216633280906007</v>
+      </c>
+      <c r="F87" t="n">
+        <v>63421.69</v>
+      </c>
+      <c r="G87" t="n">
+        <v>106.6201100000001</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.7979999999990923</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>05:50</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>311081.5802966952</v>
+      </c>
+      <c r="D88" t="n">
+        <v>19763180780.30241</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>0.007312508725477626</v>
+      </c>
+      <c r="F88" t="n">
+        <v>63530.54</v>
+      </c>
+      <c r="G88" t="n">
+        <v>175.3219700000001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>57.58200000000079</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>310881.9358526684</v>
+      </c>
+      <c r="D89" t="n">
+        <v>19752819549.0262</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>0.007435051646867324</v>
+      </c>
+      <c r="F89" t="n">
+        <v>63538.01</v>
+      </c>
+      <c r="G89" t="n">
+        <v>177.1748000000001</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-11.06499999999895</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>310413.3897112684</v>
+      </c>
+      <c r="D90" t="n">
+        <v>19750840370.38932</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>0.007528150956610794</v>
+      </c>
+      <c r="F90" t="n">
+        <v>63627.54</v>
+      </c>
+      <c r="G90" t="n">
+        <v>189.4762200000001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>170.8790000000009</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>310896.9821751352</v>
+      </c>
+      <c r="D91" t="n">
+        <v>19779421454.47319</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>0.007691279210057879</v>
+      </c>
+      <c r="F91" t="n">
+        <v>63620.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>129.7226100000001</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-12.55999999999915</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>311360.249478055</v>
+      </c>
+      <c r="D92" t="n">
+        <v>19819963608.78754</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>0.007747447435018732</v>
+      </c>
+      <c r="F92" t="n">
+        <v>63656.05</v>
+      </c>
+      <c r="G92" t="n">
+        <v>142.2354200000001</v>
+      </c>
+      <c r="H92" t="n">
+        <v>102.4510000000008</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>311535.1584671618</v>
+      </c>
+      <c r="D93" t="n">
+        <v>19827592853.61082</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>0.007785168673516728</v>
+      </c>
+      <c r="F93" t="n">
+        <v>63644.8</v>
+      </c>
+      <c r="G93" t="n">
+        <v>143.7855200000001</v>
+      </c>
+      <c r="H93" t="n">
+        <v>178.9490000000009</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>311667.6395910187</v>
+      </c>
+      <c r="D94" t="n">
+        <v>19823336598.63472</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>0.007889777469922634</v>
+      </c>
+      <c r="F94" t="n">
+        <v>63604.09</v>
+      </c>
+      <c r="G94" t="n">
+        <v>104.8783000000001</v>
+      </c>
+      <c r="H94" t="n">
+        <v>9.99600000000089</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>311586.3260569111</v>
+      </c>
+      <c r="D95" t="n">
+        <v>19846802624.52101</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>0.007957439288816046</v>
+      </c>
+      <c r="F95" t="n">
+        <v>63696</v>
+      </c>
+      <c r="G95" t="n">
+        <v>113.3526300000001</v>
+      </c>
+      <c r="H95" t="n">
+        <v>141.098000000001</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>311833.7816622648</v>
+      </c>
+      <c r="D96" t="n">
+        <v>19870045449.1817</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>0.008201123725146803</v>
+      </c>
+      <c r="F96" t="n">
+        <v>63719.99</v>
+      </c>
+      <c r="G96" t="n">
+        <v>134.7848200000001</v>
+      </c>
+      <c r="H96" t="n">
+        <v>612.2320000000008</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/oi_funding_history.xlsx
+++ b/oi_funding_history.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Veri" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Durum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gunluk_Ozet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sinyal_Performans" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,31 +463,6 @@
           <t>cvd_perp_btc</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>funding_durum</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>oi_durum</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>fiyat_durum</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>cvd_durum</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>genel_durum</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -515,31 +493,6 @@
       <c r="H2" t="n">
         <v>-74.93799999999942</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Pozitif</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -570,31 +523,6 @@
       <c r="H3" t="n">
         <v>-198.1839999999995</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Pozitif</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -625,31 +553,6 @@
       <c r="H4" t="n">
         <v>-254.9979999999994</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Pozitif</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -680,31 +583,6 @@
       <c r="H5" t="n">
         <v>-289.0939999999996</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Pozitif</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -735,31 +613,6 @@
       <c r="H6" t="n">
         <v>-314.7029999999995</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,31 +643,6 @@
       <c r="H7" t="n">
         <v>-398.9959999999996</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -845,31 +673,6 @@
       <c r="H8" t="n">
         <v>-657.7179999999996</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,31 +703,6 @@
       <c r="H9" t="n">
         <v>-557.6139999999998</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -955,31 +733,6 @@
       <c r="H10" t="n">
         <v>-532.5639999999999</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1010,31 +763,6 @@
       <c r="H11" t="n">
         <v>-336.955999999999</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1065,31 +793,6 @@
       <c r="H12" t="n">
         <v>-467.7109999999991</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1120,31 +823,6 @@
       <c r="H13" t="n">
         <v>-552.0339999999992</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1175,31 +853,6 @@
       <c r="H14" t="n">
         <v>-366.2589999999989</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1230,31 +883,6 @@
       <c r="H15" t="n">
         <v>-112.024999999999</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1285,31 +913,6 @@
       <c r="H16" t="n">
         <v>-121.022999999999</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1340,31 +943,6 @@
       <c r="H17" t="n">
         <v>-255.578999999999</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1395,31 +973,6 @@
       <c r="H18" t="n">
         <v>-130.3249999999987</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1450,31 +1003,6 @@
       <c r="H19" t="n">
         <v>-103.2069999999987</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1505,31 +1033,6 @@
       <c r="H20" t="n">
         <v>299.6400000000015</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1560,31 +1063,6 @@
       <c r="H21" t="n">
         <v>265.6530000000009</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1615,31 +1093,6 @@
       <c r="H22" t="n">
         <v>249.3240000000012</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1670,31 +1123,6 @@
       <c r="H23" t="n">
         <v>370.1110000000015</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1725,31 +1153,6 @@
       <c r="H24" t="n">
         <v>649.3720000000005</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1780,31 +1183,6 @@
       <c r="H25" t="n">
         <v>540.0760000000007</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1835,31 +1213,6 @@
       <c r="H26" t="n">
         <v>784.7780000000009</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1890,31 +1243,6 @@
       <c r="H27" t="n">
         <v>608.8840000000007</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1945,31 +1273,6 @@
       <c r="H28" t="n">
         <v>663.7940000000015</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2000,31 +1303,6 @@
       <c r="H29" t="n">
         <v>582.4580000000014</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2055,31 +1333,6 @@
       <c r="H30" t="n">
         <v>674.6360000000016</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2110,31 +1363,6 @@
       <c r="H31" t="n">
         <v>829.4370000000015</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2165,31 +1393,6 @@
       <c r="H32" t="n">
         <v>904.9710000000013</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2220,31 +1423,6 @@
       <c r="H33" t="n">
         <v>1025.227000000001</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2275,31 +1453,6 @@
       <c r="H34" t="n">
         <v>976.6420000000028</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Long Squeeze (Zayıf Temel)</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2330,31 +1483,6 @@
       <c r="H35" t="n">
         <v>367.1140000000007</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2385,31 +1513,6 @@
       <c r="H36" t="n">
         <v>819.7230000000034</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2440,31 +1543,6 @@
       <c r="H37" t="n">
         <v>521.7400000000035</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2495,31 +1573,6 @@
       <c r="H38" t="n">
         <v>636.7420000000031</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2550,31 +1603,6 @@
       <c r="H39" t="n">
         <v>929.6680000000035</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2605,31 +1633,6 @@
       <c r="H40" t="n">
         <v>-81.7039999999979</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Short (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2660,31 +1663,6 @@
       <c r="H41" t="n">
         <v>-300.3409999999965</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Short (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2715,31 +1693,6 @@
       <c r="H42" t="n">
         <v>570.0260000000037</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2770,31 +1723,6 @@
       <c r="H43" t="n">
         <v>520.5620000000038</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2825,31 +1753,6 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Nötr (Zayıf Sinyal)</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2880,31 +1783,6 @@
       <c r="H45" t="n">
         <v>1202.955000000004</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2935,31 +1813,6 @@
       <c r="H46" t="n">
         <v>1442.572000000004</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2990,31 +1843,6 @@
       <c r="H47" t="n">
         <v>1647.024000000004</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3045,31 +1873,6 @@
       <c r="H48" t="n">
         <v>1131.416000000004</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3100,31 +1903,6 @@
       <c r="H49" t="n">
         <v>1167.723000000004</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3155,31 +1933,6 @@
       <c r="H50" t="n">
         <v>1172.556000000004</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3210,31 +1963,6 @@
       <c r="H51" t="n">
         <v>1151.758000000004</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3265,31 +1993,6 @@
       <c r="H52" t="n">
         <v>1199.735000000004</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3320,31 +2023,6 @@
       <c r="H53" t="n">
         <v>1254.902000000004</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3375,31 +2053,6 @@
       <c r="H54" t="n">
         <v>1291.070000000004</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3430,31 +2083,6 @@
       <c r="H55" t="n">
         <v>1206.984000000004</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3485,31 +2113,6 @@
       <c r="H56" t="n">
         <v>1284.595000000004</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3540,31 +2143,6 @@
       <c r="H57" t="n">
         <v>1141.058000000004</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3595,31 +2173,6 @@
       <c r="H58" t="n">
         <v>1180.065000000004</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3650,31 +2203,6 @@
       <c r="H59" t="n">
         <v>1196.896000000004</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3705,31 +2233,6 @@
       <c r="H60" t="n">
         <v>775.572000000004</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3760,31 +2263,6 @@
       <c r="H61" t="n">
         <v>844.9780000000039</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3815,31 +2293,6 @@
       <c r="H62" t="n">
         <v>877.6760000000038</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Long Trap (Devam Riski)</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3870,31 +2323,6 @@
       <c r="H63" t="n">
         <v>933.9840000000038</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3925,31 +2353,6 @@
       <c r="H64" t="n">
         <v>1144.168000000004</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3980,31 +2383,6 @@
       <c r="H65" t="n">
         <v>0</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Nötr (Zayıf Sinyal)</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4035,31 +2413,6 @@
       <c r="H66" t="n">
         <v>1397.437000000004</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4090,31 +2443,6 @@
       <c r="H67" t="n">
         <v>1242.345000000003</v>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4145,31 +2473,6 @@
       <c r="H68" t="n">
         <v>878.4750000000033</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Veri Bekleniyor</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4200,31 +2503,6 @@
       <c r="H69" t="n">
         <v>981.1230000000035</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4255,31 +2533,6 @@
       <c r="H70" t="n">
         <v>915.0760000000038</v>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4310,31 +2563,6 @@
       <c r="H71" t="n">
         <v>832.1960000000038</v>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4365,31 +2593,6 @@
       <c r="H72" t="n">
         <v>674.9420000000036</v>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4420,31 +2623,6 @@
       <c r="H73" t="n">
         <v>696.639000000004</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4475,31 +2653,6 @@
       <c r="H74" t="n">
         <v>541.0600000000042</v>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4530,31 +2683,6 @@
       <c r="H75" t="n">
         <v>588.5630000000042</v>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4585,31 +2713,6 @@
       <c r="H76" t="n">
         <v>573.2510000000042</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4640,31 +2743,6 @@
       <c r="H77" t="n">
         <v>65.58500000000001</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Spot Short / Perp Long (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4695,31 +2773,6 @@
       <c r="H78" t="n">
         <v>377.1559999999999</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4750,31 +2803,6 @@
       <c r="H79" t="n">
         <v>615.4929999999999</v>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4805,31 +2833,6 @@
       <c r="H80" t="n">
         <v>338.3040000000001</v>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4860,31 +2863,6 @@
       <c r="H81" t="n">
         <v>312.3480000000005</v>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4915,31 +2893,6 @@
       <c r="H82" t="n">
         <v>417.2880000000005</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4970,31 +2923,6 @@
       <c r="H83" t="n">
         <v>318.0770000000005</v>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Düşüyor</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5025,31 +2953,6 @@
       <c r="H84" t="n">
         <v>218.1520000000005</v>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5080,31 +2983,6 @@
       <c r="H85" t="n">
         <v>167.1890000000009</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5135,31 +3013,6 @@
       <c r="H86" t="n">
         <v>83.17400000000089</v>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5190,31 +3043,6 @@
       <c r="H87" t="n">
         <v>-0.7979999999990923</v>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5245,31 +3073,6 @@
       <c r="H88" t="n">
         <v>57.58200000000079</v>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5300,31 +3103,6 @@
       <c r="H89" t="n">
         <v>-11.06499999999895</v>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5355,31 +3133,6 @@
       <c r="H90" t="n">
         <v>170.8790000000009</v>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Artıyor</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5410,31 +3163,6 @@
       <c r="H91" t="n">
         <v>-12.55999999999915</v>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Short (Diverjans)</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5465,31 +3193,6 @@
       <c r="H92" t="n">
         <v>102.4510000000008</v>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5520,31 +3223,6 @@
       <c r="H93" t="n">
         <v>178.9490000000009</v>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5575,31 +3253,6 @@
       <c r="H94" t="n">
         <v>9.99600000000089</v>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5630,31 +3283,6 @@
       <c r="H95" t="n">
         <v>141.098000000001</v>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Spot Long / Perp Long (Uyumlu)</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5685,29 +3313,6067 @@
       <c r="H96" t="n">
         <v>612.2320000000008</v>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Aşırı Pozitif</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Nötr</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>309486.1156393677</v>
+      </c>
+      <c r="D97" t="n">
+        <v>19774095422.10313</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>0.008466918098920528</v>
+      </c>
+      <c r="F97" t="n">
+        <v>63893.32</v>
+      </c>
+      <c r="G97" t="n">
+        <v>166.3008300000001</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1854.993000000002</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>309389.467651143</v>
+      </c>
+      <c r="D98" t="n">
+        <v>19750634671.70646</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>0.008533244785589724</v>
+      </c>
+      <c r="F98" t="n">
+        <v>63837.45</v>
+      </c>
+      <c r="G98" t="n">
+        <v>144.7618300000002</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1431.503</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>309294.9437267624</v>
+      </c>
+      <c r="D99" t="n">
+        <v>19744111819.39892</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>0.008646613547682955</v>
+      </c>
+      <c r="F99" t="n">
+        <v>63835.87</v>
+      </c>
+      <c r="G99" t="n">
+        <v>144.1259600000002</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1356.646</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>309312.9523908608</v>
+      </c>
+      <c r="D100" t="n">
+        <v>19743303467.15055</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>0.008795644931066871</v>
+      </c>
+      <c r="F100" t="n">
+        <v>63829.54</v>
+      </c>
+      <c r="G100" t="n">
+        <v>144.9051200000002</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1289.898</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>309126.0263258146</v>
+      </c>
+      <c r="D101" t="n">
+        <v>19717164630.2347</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>0.008757525644361762</v>
+      </c>
+      <c r="F101" t="n">
+        <v>63783.58</v>
+      </c>
+      <c r="G101" t="n">
+        <v>135.5130000000002</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1059.081</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>308926.8223654798</v>
+      </c>
+      <c r="D102" t="n">
+        <v>19740176807.69627</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>0.008661512092902781</v>
+      </c>
+      <c r="F102" t="n">
+        <v>63899.2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>130.9260100000002</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1111.835</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>308633.8136229755</v>
+      </c>
+      <c r="D103" t="n">
+        <v>19716166886.22988</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>0.008623406047994287</v>
+      </c>
+      <c r="F103" t="n">
+        <v>63882.07</v>
+      </c>
+      <c r="G103" t="n">
+        <v>110.3468800000002</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1031.844000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>308596.4056579809</v>
+      </c>
+      <c r="D104" t="n">
+        <v>19714039494.93634</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>0.008487421683257442</v>
+      </c>
+      <c r="F104" t="n">
+        <v>63882.92</v>
+      </c>
+      <c r="G104" t="n">
+        <v>237.0544700000002</v>
+      </c>
+      <c r="H104" t="n">
+        <v>875.8340000000006</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>308470.7179487363</v>
+      </c>
+      <c r="D105" t="n">
+        <v>19710044994.05246</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>0.008235910693036967</v>
+      </c>
+      <c r="F105" t="n">
+        <v>63896</v>
+      </c>
+      <c r="G105" t="n">
+        <v>309.1637300000002</v>
+      </c>
+      <c r="H105" t="n">
+        <v>828.4750000000006</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>308413.6634369839</v>
+      </c>
+      <c r="D106" t="n">
+        <v>19694106070.34493</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>0.007887856735586502</v>
+      </c>
+      <c r="F106" t="n">
+        <v>63856.14</v>
+      </c>
+      <c r="G106" t="n">
+        <v>334.8912600000001</v>
+      </c>
+      <c r="H106" t="n">
+        <v>724.9220000000005</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>308379.7349921112</v>
+      </c>
+      <c r="D107" t="n">
+        <v>19709881063.80099</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>0.007556587249903233</v>
+      </c>
+      <c r="F107" t="n">
+        <v>63914.32</v>
+      </c>
+      <c r="G107" t="n">
+        <v>379.9066100000001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>836.6060000000007</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>308328.5099053101</v>
+      </c>
+      <c r="D108" t="n">
+        <v>19678139075.8916</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>0.005408156306572827</v>
+      </c>
+      <c r="F108" t="n">
+        <v>63821.99</v>
+      </c>
+      <c r="G108" t="n">
+        <v>352.9946500000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>634.1980000000007</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>308088.6121563943</v>
+      </c>
+      <c r="D109" t="n">
+        <v>19648351240.27404</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>0.006610485458539163</v>
+      </c>
+      <c r="F109" t="n">
+        <v>63775</v>
+      </c>
+      <c r="G109" t="n">
+        <v>284.0472900000001</v>
+      </c>
+      <c r="H109" t="n">
+        <v>316.5690000000006</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>307965.165078062</v>
+      </c>
+      <c r="D110" t="n">
+        <v>19643869099.32091</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>0.006917191761662638</v>
+      </c>
+      <c r="F110" t="n">
+        <v>63786.01</v>
+      </c>
+      <c r="G110" t="n">
+        <v>301.90856</v>
+      </c>
+      <c r="H110" t="n">
+        <v>215.6890000000005</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>307964.2766060078</v>
+      </c>
+      <c r="D111" t="n">
+        <v>19624983491.36189</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>0.006584064897034521</v>
+      </c>
+      <c r="F111" t="n">
+        <v>63724.87</v>
+      </c>
+      <c r="G111" t="n">
+        <v>297.8576800000001</v>
+      </c>
+      <c r="H111" t="n">
+        <v>53.28000000000105</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>307861.9952811083</v>
+      </c>
+      <c r="D112" t="n">
+        <v>19600341791.56704</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>0.006507891135965091</v>
+      </c>
+      <c r="F112" t="n">
+        <v>63666</v>
+      </c>
+      <c r="G112" t="n">
+        <v>308.3941800000001</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-275.444999999999</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>308136.8086770111</v>
+      </c>
+      <c r="D113" t="n">
+        <v>19629528771.7518</v>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>0.00683147361158378</v>
+      </c>
+      <c r="F113" t="n">
+        <v>63703.94</v>
+      </c>
+      <c r="G113" t="n">
+        <v>316.9044000000001</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-190.504999999999</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>308197.1254281128</v>
+      </c>
+      <c r="D114" t="n">
+        <v>19640166933.06066</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>0.007024121056685503</v>
+      </c>
+      <c r="F114" t="n">
+        <v>63725.99</v>
+      </c>
+      <c r="G114" t="n">
+        <v>340.3690700000001</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-116.895999999999</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>306957.1257209898</v>
+      </c>
+      <c r="D115" t="n">
+        <v>19545188023.15831</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>0.007092364838014054</v>
+      </c>
+      <c r="F115" t="n">
+        <v>63674</v>
+      </c>
+      <c r="G115" t="n">
+        <v>356.91657</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-84.6359999999986</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>307904.7812703077</v>
+      </c>
+      <c r="D116" t="n">
+        <v>19598139327.85508</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>0.007133128655817612</v>
+      </c>
+      <c r="F116" t="n">
+        <v>63650</v>
+      </c>
+      <c r="G116" t="n">
+        <v>313.5127200000001</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-324.2589999999989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>307905.1078859827</v>
+      </c>
+      <c r="D117" t="n">
+        <v>19587072454.00782</v>
+      </c>
+      <c r="E117" s="1" t="n">
+        <v>0.007204637183124747</v>
+      </c>
+      <c r="F117" t="n">
+        <v>63613.99</v>
+      </c>
+      <c r="G117" t="n">
+        <v>309.8850500000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-448.8229999999987</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>308030.6002815129</v>
+      </c>
+      <c r="D118" t="n">
+        <v>19603067401.91548</v>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>0.007345675719214654</v>
+      </c>
+      <c r="F118" t="n">
+        <v>63640</v>
+      </c>
+      <c r="G118" t="n">
+        <v>295.2454200000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-545.5879999999981</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>308011.8423127224</v>
+      </c>
+      <c r="D119" t="n">
+        <v>19606287454.48199</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>0.007457300159684461</v>
+      </c>
+      <c r="F119" t="n">
+        <v>63654.33</v>
+      </c>
+      <c r="G119" t="n">
+        <v>307.00019</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-351.1509999999989</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>308018.9468688135</v>
+      </c>
+      <c r="D120" t="n">
+        <v>19597699334.14933</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>0.007475201127179702</v>
+      </c>
+      <c r="F120" t="n">
+        <v>63624.98</v>
+      </c>
+      <c r="G120" t="n">
+        <v>306.68283</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-396.6949999999989</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>306826.2229055439</v>
+      </c>
+      <c r="D121" t="n">
+        <v>19452785600.47371</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>0.0073445807031562</v>
+      </c>
+      <c r="F121" t="n">
+        <v>63400.01</v>
+      </c>
+      <c r="G121" t="n">
+        <v>235.1286200000001</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-1331.754999999999</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>306642.3894568972</v>
+      </c>
+      <c r="D122" t="n">
+        <v>19466520547.8382</v>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>0.007344557090410166</v>
+      </c>
+      <c r="F122" t="n">
+        <v>63482.81</v>
+      </c>
+      <c r="G122" t="n">
+        <v>260.0817</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-943.0979999999984</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>307256.4180190809</v>
+      </c>
+      <c r="D123" t="n">
+        <v>19504557529.18257</v>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>0.007403482415267916</v>
+      </c>
+      <c r="F123" t="n">
+        <v>63479.74</v>
+      </c>
+      <c r="G123" t="n">
+        <v>276.28804</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-843.2839999999995</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>307639.7720424293</v>
+      </c>
+      <c r="D124" t="n">
+        <v>19554522212.32154</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>0.00746832014822341</v>
+      </c>
+      <c r="F124" t="n">
+        <v>63563.05</v>
+      </c>
+      <c r="G124" t="n">
+        <v>296.4200300000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-427.5519999999995</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>307714.203109377</v>
+      </c>
+      <c r="D125" t="n">
+        <v>19582833417.33576</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>0.007350448480431927</v>
+      </c>
+      <c r="F125" t="n">
+        <v>63639.68</v>
+      </c>
+      <c r="G125" t="n">
+        <v>323.90933</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-152.5549999999996</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>308015.9562654121</v>
+      </c>
+      <c r="D126" t="n">
+        <v>19601211408.86203</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>0.007254147750246115</v>
+      </c>
+      <c r="F126" t="n">
+        <v>63637</v>
+      </c>
+      <c r="G126" t="n">
+        <v>315.9910300000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-180.7909999999995</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>308066.9673718163</v>
+      </c>
+      <c r="D127" t="n">
+        <v>19650362661.44835</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>0.00727411472965079</v>
+      </c>
+      <c r="F127" t="n">
+        <v>63786.01</v>
+      </c>
+      <c r="G127" t="n">
+        <v>326.43824</v>
+      </c>
+      <c r="H127" t="n">
+        <v>199.3250000000005</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>307580.2376127788</v>
+      </c>
+      <c r="D128" t="n">
+        <v>19587373904.495</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>0.007004592103104794</v>
+      </c>
+      <c r="F128" t="n">
+        <v>63682.16</v>
+      </c>
+      <c r="G128" t="n">
+        <v>302.17803</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-148.3269999999995</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>307696.7262367959</v>
+      </c>
+      <c r="D129" t="n">
+        <v>19616709389.49768</v>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>0.007002297420392321</v>
+      </c>
+      <c r="F129" t="n">
+        <v>63753.39</v>
+      </c>
+      <c r="G129" t="n">
+        <v>290.80891</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-47.9239999999993</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>307164.3093643603</v>
+      </c>
+      <c r="D130" t="n">
+        <v>19592165236.85327</v>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>0.007022517345052779</v>
+      </c>
+      <c r="F130" t="n">
+        <v>63783.99</v>
+      </c>
+      <c r="G130" t="n">
+        <v>265.11482</v>
+      </c>
+      <c r="H130" t="n">
+        <v>43.56799999999998</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>307191.4475339273</v>
+      </c>
+      <c r="D131" t="n">
+        <v>19588154809.43514</v>
+      </c>
+      <c r="E131" s="1" t="n">
+        <v>0.006942707150800723</v>
+      </c>
+      <c r="F131" t="n">
+        <v>63765.3</v>
+      </c>
+      <c r="G131" t="n">
+        <v>265.0152200000001</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-30.92599999999888</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G131"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tarih</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>saat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>funding_durum</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>oi_durum</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fiyat_durum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cvd_durum</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>genel_durum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pozitif</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pozitif</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pozitif</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pozitif</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Spot Long / Perp Long (Uyumlu)</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>İşlem Açma</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Long Squeeze (Zayıf Temel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Short (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Short (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Nötr (Zayıf Sinyal)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>19:49</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>22:25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>22:55</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>23:41</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>23:56</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Nötr (Zayıf Sinyal)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>00:42</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Veri Bekleniyor</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>00:58</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>01:29</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>01:59</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spot Short / Perp Long (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>03:31</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>04:48</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>05:50</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Artıyor</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Düşüyor</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Long (Uyumlu)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Aşırı Pozitif</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Nötr</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Spot Long / Perp Short (Diverjans)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tarih</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>genel_durum</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Long Squeeze (Zayıf Temel)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Long Trap (Devam Riski)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>12.08.2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>13.08.2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>İşlem Açma</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>kapanis_tarih</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>kapanis_saat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sinyal</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>yon</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>giris_tarih</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>giris_saat</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>giris_fiyat</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cikis_fiyat</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>kar_yuzde</t>
         </is>
       </c>
     </row>
